--- a/data/trans_dic/P39A3_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P39A3_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar en el pecho es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar en el pecho es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 93,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>89,63; 97,72</t>
+          <t>89,94; 97,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>96,68; 99,01</t>
+          <t>96,67; 98,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94,0; 98,01</t>
+          <t>93,96; 98,05</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>95,31; 98,89</t>
+          <t>95,39; 98,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>94,35; 97,42</t>
+          <t>94,46; 97,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>95,5; 97,86</t>
+          <t>95,69; 97,95</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>91,58; 96,33</t>
+          <t>91,57; 96,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>95,06; 98,37</t>
+          <t>95,16; 98,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>94,31; 96,94</t>
+          <t>94,14; 96,98</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>94,9; 99,15</t>
+          <t>95,16; 99,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,55; 97,43</t>
+          <t>44,58; 97,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59,69; 97,7</t>
+          <t>59,54; 97,63</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>57,48; 69,59</t>
+          <t>57,33; 69,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>53,32; 63,03</t>
+          <t>53,19; 63,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56,77; 64,33</t>
+          <t>56,75; 64,54</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>85,78; 93,84</t>
+          <t>85,97; 93,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>90,73; 95,85</t>
+          <t>90,52; 95,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>89,66; 94,28</t>
+          <t>89,55; 94,26</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>77,64; 84,87</t>
+          <t>77,77; 84,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>77,78; 92,43</t>
+          <t>77,8; 92,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79,25; 88,88</t>
+          <t>79,15; 88,72</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>97,01; 99,52</t>
+          <t>97,09; 99,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>96,76; 98,73</t>
+          <t>96,79; 98,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>97,34; 99,02</t>
+          <t>97,23; 99,0</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>90,76; 93,69</t>
+          <t>90,85; 94,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>82,69; 91,78</t>
+          <t>82,87; 91,77</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>87,25; 92,12</t>
+          <t>86,62; 92,13</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar en el pecho es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar en el pecho es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 93,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>278483; 303640</t>
+          <t>279463; 303481</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>274418; 281035</t>
+          <t>274394; 280948</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>558920; 582758</t>
+          <t>558631; 582985</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>487225; 505521</t>
+          <t>487630; 505873</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>471116; 486454</t>
+          <t>471640; 486577</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>965009; 988857</t>
+          <t>967019; 989767</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>272829; 286985</t>
+          <t>272793; 286860</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>304398; 314999</t>
+          <t>304718; 314955</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>582976; 599237</t>
+          <t>581914; 599437</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>236611; 247196</t>
+          <t>237257; 247463</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>161210; 369090</t>
+          <t>168901; 369000</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>374945; 613728</t>
+          <t>374019; 613278</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>100942; 122199</t>
+          <t>100668; 121805</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>110268; 130347</t>
+          <t>110008; 130613</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>217093; 246016</t>
+          <t>217019; 246798</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>212900; 232884</t>
+          <t>213350; 232797</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>208218; 219983</t>
+          <t>207752; 220153</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>428273; 450373</t>
+          <t>427767; 450276</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>468139; 511729</t>
+          <t>468911; 510639</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>641063; 761745</t>
+          <t>641193; 765164</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1131008; 1268379</t>
+          <t>1129639; 1266075</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>838446; 860153</t>
+          <t>839134; 860199</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>645973; 659132</t>
+          <t>646156; 658630</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1491142; 1516839</t>
+          <t>1489531; 1516613</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2958826; 3054492</t>
+          <t>2961758; 3072985</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2820047; 3129949</t>
+          <t>2825987; 3129795</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5820202; 6145157</t>
+          <t>5778210; 6145238</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P39A3_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P39A3_2023-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>89,94; 97,67</t>
+          <t>92,45; 98,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>96,67; 98,98</t>
+          <t>96,93; 99,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93,96; 98,05</t>
+          <t>95,55; 98,33</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>95,39; 98,96</t>
+          <t>95,24; 98,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>94,46; 97,45</t>
+          <t>94,24; 97,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>95,69; 97,95</t>
+          <t>95,29; 97,67</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>91,57; 96,29</t>
+          <t>90,81; 96,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>95,16; 98,36</t>
+          <t>94,66; 98,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>94,14; 96,98</t>
+          <t>93,79; 96,74</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>95,16; 99,26</t>
+          <t>91,3; 98,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,58; 97,4</t>
+          <t>93,97; 98,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59,54; 97,63</t>
+          <t>94,0; 97,79</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>61,29%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>57,33; 69,36</t>
+          <t>58,44; 69,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>53,19; 63,16</t>
+          <t>54,23; 63,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56,75; 64,54</t>
+          <t>57,74; 65,29</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,24%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>85,97; 93,8</t>
+          <t>86,84; 94,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>90,52; 95,93</t>
+          <t>90,36; 95,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>89,55; 94,26</t>
+          <t>89,52; 94,29</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>79,33%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>77,77; 84,69</t>
+          <t>76,75; 83,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>77,8; 92,84</t>
+          <t>75,6; 80,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79,15; 88,72</t>
+          <t>77,0; 81,39</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>97,09; 99,53</t>
+          <t>95,91; 98,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>96,79; 98,65</t>
+          <t>96,6; 98,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>97,23; 99,0</t>
+          <t>96,77; 98,42</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,63%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>90,85; 94,26</t>
+          <t>89,77; 91,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>82,87; 91,77</t>
+          <t>89,57; 91,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>86,62; 92,13</t>
+          <t>89,92; 91,27</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>296267</t>
+          <t>306298</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>278490</t>
+          <t>306737</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>574757</t>
+          <t>613035</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>279463; 303481</t>
+          <t>294050; 312310</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>274394; 280948</t>
+          <t>302651; 309461</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>558631; 582985</t>
+          <t>602248; 619743</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>499427</t>
+          <t>508231</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>480170</t>
+          <t>508839</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>979597</t>
+          <t>1017070</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>487630; 505873</t>
+          <t>497137; 515432</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>471640; 486577</t>
+          <t>499101; 515665</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>967019; 989767</t>
+          <t>1002068; 1027137</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>281281</t>
+          <t>279114</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>310776</t>
+          <t>315149</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>592058</t>
+          <t>594263</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>272793; 286860</t>
+          <t>269758; 285767</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>304718; 314955</t>
+          <t>308214; 319736</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>581914; 599437</t>
+          <t>583994; 602385</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>243994</t>
+          <t>277560</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>299132</t>
+          <t>332298</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>543127</t>
+          <t>609860</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>237257; 247463</t>
+          <t>262740; 283584</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>168901; 369000</t>
+          <t>323722; 337800</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>374019; 613278</t>
+          <t>594383; 618304</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>111796</t>
+          <t>127846</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>120427</t>
+          <t>132839</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>232224</t>
+          <t>260686</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>100668; 121805</t>
+          <t>116906; 139239</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>110008; 130613</t>
+          <t>122185; 143671</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>217019; 246798</t>
+          <t>245576; 277713</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>225303</t>
+          <t>222613</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>215009</t>
+          <t>219717</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>440313</t>
+          <t>442330</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>213350; 232797</t>
+          <t>212218; 230553</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>207752; 220153</t>
+          <t>212472; 225359</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>427767; 450276</t>
+          <t>429270; 452149</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>491548</t>
+          <t>557895</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>692788</t>
+          <t>575827</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1184336</t>
+          <t>1133722</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>468911; 510639</t>
+          <t>532597; 581063</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>641193; 765164</t>
+          <t>555808; 594787</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1129639; 1266075</t>
+          <t>1100469; 1163281</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>850757</t>
+          <t>698654</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>653569</t>
+          <t>749425</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1504326</t>
+          <t>1448079</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>839134; 860199</t>
+          <t>685279; 705688</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>646156; 658630</t>
+          <t>740458; 755321</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1489531; 1516613</t>
+          <t>1433213; 1457655</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>3000375</t>
+          <t>2978214</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3050363</t>
+          <t>3140829</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6050738</t>
+          <t>6119043</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2961758; 3072985</t>
+          <t>2942361; 3011350</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2825987; 3129795</t>
+          <t>3111738; 3166450</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5778210; 6145238</t>
+          <t>6071379; 6162176</t>
         </is>
       </c>
     </row>
